--- a/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/03_WIM3 - Müşteri Koruma, Tier-N ve TSB/EKG-KLT-FRM-41_garanti_kriz_yonetimi_kontrol_listesi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/03_WIM3 - Müşteri Koruma, Tier-N ve TSB/EKG-KLT-FRM-41_garanti_kriz_yonetimi_kontrol_listesi.xlsx
@@ -1062,7 +1062,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-41&amp;C&amp;"Arial,Regular"&amp;11Garanti Kriz Yönetimi Kontrol Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 22.09.2026
+Revizyon nedeni: Kriz formu ürün koruma ve yetkili çıkışa göre düzenlendi; açık/kapalı termin formülleri eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1240,7 +1241,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-FRM-41&amp;C&amp;"Arial,Regular"&amp;11Garanti Kriz Yönetimi Kontrol Listesi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 10.06.2026 | Revizyon: 22.09.2026
+Revizyon nedeni: Kriz formu ürün koruma ve yetkili çıkışa göre düzenlendi; açık/kapalı termin formülleri eklendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>